--- a/PLANILHA EMISSAO NOVA 2025-2.xlsx
+++ b/PLANILHA EMISSAO NOVA 2025-2.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projetos\datavix\RoboNotaMaceio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Robo maceio\main novo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEE906A9-7829-4AB5-B98A-1845DD0EDE7D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F5735F-5A46-466A-8D93-DCABA8F7BEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3765" yWindow="2355" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MODELO NOVO" sheetId="34" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MODELO NOVO'!$F$2:$I$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MODELO NOVO'!$F$2:$I$36</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="58">
   <si>
     <t>VALOR</t>
   </si>
@@ -39,12 +39,6 @@
     <t>STATUS NF</t>
   </si>
   <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>MAQUININHA</t>
-  </si>
-  <si>
     <t>FORMA</t>
   </si>
   <si>
@@ -57,9 +51,6 @@
     <t>NOME</t>
   </si>
   <si>
-    <t>ARTHUR CORREIA LIMA</t>
-  </si>
-  <si>
     <t>CEP</t>
   </si>
   <si>
@@ -67,6 +58,150 @@
   </si>
   <si>
     <t>EMISSAO DE NOTA FISCAL</t>
+  </si>
+  <si>
+    <t>EUDES ALELUIA JUNIOR</t>
+  </si>
+  <si>
+    <t>EMITIR</t>
+  </si>
+  <si>
+    <t>LINK</t>
+  </si>
+  <si>
+    <t>CARLOS ALBERTO VANDERLEI VANGASSE</t>
+  </si>
+  <si>
+    <t>PIX</t>
+  </si>
+  <si>
+    <t>MARIA JEANE SUTERIO VIRTUOSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THACYANE TORRES DA SILVA </t>
+  </si>
+  <si>
+    <t>ELISAMA ALVES DOS ANTOS</t>
+  </si>
+  <si>
+    <t>JOSE MARIANO SOBRINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICIA SUELY PINHEIRO DA SILVA LIMA </t>
+  </si>
+  <si>
+    <t>MARCOS MAURICIO PEDROSA SOUZA PEIXOTO</t>
+  </si>
+  <si>
+    <t>LUCILENE PAULO DA SILVA</t>
+  </si>
+  <si>
+    <t>RODRIGO LEANDRO DE MOURA</t>
+  </si>
+  <si>
+    <t>MARIA CRISTINA PEIXOTO GERBASE</t>
+  </si>
+  <si>
+    <t>PAULO MARCOS DE LIMA</t>
+  </si>
+  <si>
+    <t>TERESA CRISTINA ARAUJO DE AMORIM MOREIRA</t>
+  </si>
+  <si>
+    <t>DANIEL PINTO FERNANDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAGNER CALHEIROS ANGELO </t>
+  </si>
+  <si>
+    <t>MARIANA DE CASTRO BARBOSA</t>
+  </si>
+  <si>
+    <t>ALYCE ALMEIDA RODRIGUEs</t>
+  </si>
+  <si>
+    <t>ALYSSON DAVID ARAUJOS DA SILVA</t>
+  </si>
+  <si>
+    <t>MARCIO REBELO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>NTHALIA MIRELLE DA SILVA SANTOS</t>
+  </si>
+  <si>
+    <t>ELIZIANE RIBEIRO BARROS</t>
+  </si>
+  <si>
+    <t>THALITA CRISTINA FIQUEIREDO CUNHA</t>
+  </si>
+  <si>
+    <t>EDISON CAMILO DE MORAES JUNIOR</t>
+  </si>
+  <si>
+    <t>TERESA CRISTINA BEZERRA DE ARAUJO</t>
+  </si>
+  <si>
+    <t>52147266434</t>
+  </si>
+  <si>
+    <t>47236370444</t>
+  </si>
+  <si>
+    <t>03879276463</t>
+  </si>
+  <si>
+    <t>05135276483</t>
+  </si>
+  <si>
+    <t>08742854458</t>
+  </si>
+  <si>
+    <t>02651218413</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 07285439401</t>
+  </si>
+  <si>
+    <t>10563271469</t>
+  </si>
+  <si>
+    <t>31233660497</t>
+  </si>
+  <si>
+    <t>48371866453</t>
+  </si>
+  <si>
+    <t>06663587617</t>
+  </si>
+  <si>
+    <t>06137081486</t>
+  </si>
+  <si>
+    <t>08481227471</t>
+  </si>
+  <si>
+    <t>11885565410</t>
+  </si>
+  <si>
+    <t>04642491473</t>
+  </si>
+  <si>
+    <t>2123152420</t>
+  </si>
+  <si>
+    <t>10966022459</t>
+  </si>
+  <si>
+    <t>01365220338</t>
+  </si>
+  <si>
+    <t>07610404470</t>
+  </si>
+  <si>
+    <t>67961002472</t>
+  </si>
+  <si>
+    <t>60400676400</t>
   </si>
 </sst>
 </file>
@@ -76,7 +211,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,8 +256,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -141,8 +289,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -257,6 +411,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -265,7 +467,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -273,19 +475,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -306,12 +498,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -327,6 +513,40 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -345,293 +565,7 @@
     <cellStyle name="Moeda 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -683,24 +617,260 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -716,17 +886,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{084DBA03-93C1-466C-9A90-0079D410E7CC}" name="Tabela1" displayName="Tabela1" ref="B2:I1048576" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
-  <autoFilter ref="B2:I1048576" xr:uid="{084DBA03-93C1-466C-9A90-0079D410E7CC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{084DBA03-93C1-466C-9A90-0079D410E7CC}" name="Tabela1" displayName="Tabela1" ref="B2:I1048575" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+  <autoFilter ref="B2:I1048575" xr:uid="{084DBA03-93C1-466C-9A90-0079D410E7CC}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{09160A6F-7823-49FF-830F-B93B5861BA95}" name="CPF" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{FE32E1F7-7D64-4EC7-8969-C12D85D6CE51}" name="NOME" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{ACC4B82F-E58E-4924-B215-C073FA097BA4}" name="CEP" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{C48B140D-69F2-4F39-A516-62DDFD5C1FC7}" name="Nº" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{284A46D5-9ABE-4D4A-8FB0-214E7F89FF0C}" name="VALOR" dataDxfId="6" dataCellStyle="Moeda"/>
-    <tableColumn id="6" xr3:uid="{EDD405EF-3B24-4FD1-935C-D467A41FAF2B}" name="DATA" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{2B643CE9-7390-4C50-97C4-DBCF35B959AB}" name="STATUS NF" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{C08C96E8-EEE9-4369-99CF-81FB490F3DD3}" name="FORMA" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{09160A6F-7823-49FF-830F-B93B5861BA95}" name="CPF" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{FE32E1F7-7D64-4EC7-8969-C12D85D6CE51}" name="NOME" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{ACC4B82F-E58E-4924-B215-C073FA097BA4}" name="CEP" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{C48B140D-69F2-4F39-A516-62DDFD5C1FC7}" name="Nº" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{284A46D5-9ABE-4D4A-8FB0-214E7F89FF0C}" name="VALOR" dataDxfId="8" dataCellStyle="Moeda"/>
+    <tableColumn id="6" xr3:uid="{EDD405EF-3B24-4FD1-935C-D467A41FAF2B}" name="DATA" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{2B643CE9-7390-4C50-97C4-DBCF35B959AB}" name="STATUS NF" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{C08C96E8-EEE9-4369-99CF-81FB490F3DD3}" name="FORMA" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -990,360 +1160,769 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDBF4B70-4622-4357-8ECE-72B7C1016D16}">
-  <dimension ref="B1:I38"/>
+  <dimension ref="B1:I37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="24"/>
-    <col min="2" max="2" width="12" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="18"/>
+    <col min="2" max="2" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" style="2" customWidth="1"/>
     <col min="8" max="8" width="12.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" style="12" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="24"/>
+    <col min="9" max="9" width="13.140625" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" s="22" customFormat="1" ht="21.75" customHeight="1">
-      <c r="B1" s="26" t="s">
+    <row r="1" spans="2:9" s="16" customFormat="1" ht="21.75" customHeight="1">
+      <c r="B1" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
+    </row>
+    <row r="2" spans="2:9" s="17" customFormat="1" ht="19.5" customHeight="1">
+      <c r="B2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9">
+      <c r="B3" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="28">
+        <v>57014070</v>
+      </c>
+      <c r="E3" s="28">
+        <v>225</v>
+      </c>
+      <c r="F3" s="29">
+        <v>1180.71</v>
+      </c>
+      <c r="G3" s="30">
+        <v>45901</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="28"/>
-    </row>
-    <row r="2" spans="2:9" s="23" customFormat="1" ht="19.5" customHeight="1">
-      <c r="B2" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="13" t="s">
+    </row>
+    <row r="4" spans="2:9">
+      <c r="B4" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="28">
+        <v>57025890</v>
+      </c>
+      <c r="E4" s="28">
+        <v>1212</v>
+      </c>
+      <c r="F4" s="29">
+        <v>902.72</v>
+      </c>
+      <c r="G4" s="30">
+        <v>45902</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9">
+      <c r="B5" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="28">
+        <v>57048570</v>
+      </c>
+      <c r="E5" s="28">
+        <v>38</v>
+      </c>
+      <c r="F5" s="29">
+        <v>1153.79</v>
+      </c>
+      <c r="G5" s="30">
+        <v>45904</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="28">
+        <v>57120000</v>
+      </c>
+      <c r="E6" s="28">
+        <v>422</v>
+      </c>
+      <c r="F6" s="29">
+        <v>802.82</v>
+      </c>
+      <c r="G6" s="30">
+        <v>45905</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="28">
+        <v>57039740</v>
+      </c>
+      <c r="E7" s="28">
+        <v>0</v>
+      </c>
+      <c r="F7" s="29">
+        <v>796.52</v>
+      </c>
+      <c r="G7" s="30">
+        <v>45905</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" s="27">
+        <v>36033880463</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="28">
+        <v>57038006</v>
+      </c>
+      <c r="E8" s="28">
+        <v>52</v>
+      </c>
+      <c r="F8" s="29">
+        <v>259.2</v>
+      </c>
+      <c r="G8" s="30">
+        <v>45908</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="28">
+        <v>57025510</v>
+      </c>
+      <c r="E9" s="28">
+        <v>656</v>
+      </c>
+      <c r="F9" s="29">
+        <v>60.33</v>
+      </c>
+      <c r="G9" s="30">
+        <v>45908</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" s="19" customFormat="1">
+      <c r="B10" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="32">
+        <v>57010380</v>
+      </c>
+      <c r="E10" s="32">
+        <v>523</v>
+      </c>
+      <c r="F10" s="33">
+        <v>1534.72</v>
+      </c>
+      <c r="G10" s="34">
+        <v>45909</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" s="27">
+        <v>66285712468</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="28">
+        <v>57035210</v>
+      </c>
+      <c r="E11" s="28">
+        <v>1032</v>
+      </c>
+      <c r="F11" s="29">
+        <v>116.88</v>
+      </c>
+      <c r="G11" s="30">
+        <v>45909</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="B12" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="28">
+        <v>57085160</v>
+      </c>
+      <c r="E12" s="28">
+        <v>96</v>
+      </c>
+      <c r="F12" s="29">
+        <v>524.30999999999995</v>
+      </c>
+      <c r="G12" s="30">
+        <v>45909</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="28">
+        <v>57160000</v>
+      </c>
+      <c r="E13" s="28">
+        <v>262</v>
+      </c>
+      <c r="F13" s="29">
+        <v>60.33</v>
+      </c>
+      <c r="G13" s="30">
+        <v>45911</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="28">
+        <v>57025870</v>
+      </c>
+      <c r="E14" s="28">
+        <v>148</v>
+      </c>
+      <c r="F14" s="29">
+        <v>2091.08</v>
+      </c>
+      <c r="G14" s="30">
+        <v>45912</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" s="27">
+        <v>15393666420</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="28">
+        <v>57044131</v>
+      </c>
+      <c r="E15" s="28">
+        <v>1</v>
+      </c>
+      <c r="F15" s="29">
+        <v>1518.98</v>
+      </c>
+      <c r="G15" s="30">
+        <v>45912</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="28">
+        <v>57048066</v>
+      </c>
+      <c r="E16" s="28">
+        <v>0</v>
+      </c>
+      <c r="F16" s="29">
+        <v>346.89</v>
+      </c>
+      <c r="G16" s="30">
+        <v>45912</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="28">
+        <v>57014120</v>
+      </c>
+      <c r="E17" s="28">
         <v>8</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="14" t="s">
+      <c r="F17" s="29">
+        <v>541.76</v>
+      </c>
+      <c r="G17" s="30">
+        <v>45915</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="28">
+        <v>57045430</v>
+      </c>
+      <c r="E18" s="28">
         <v>0</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="20" t="s">
+      <c r="F18" s="29">
+        <v>848.56</v>
+      </c>
+      <c r="G18" s="30">
+        <v>45915</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="28">
+        <v>57300970</v>
+      </c>
+      <c r="E19" s="28">
+        <v>126</v>
+      </c>
+      <c r="F19" s="35">
+        <v>400.12</v>
+      </c>
+      <c r="G19" s="30">
+        <v>45915</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="28">
+        <v>57010030</v>
+      </c>
+      <c r="E20" s="28">
+        <v>4</v>
+      </c>
+      <c r="F20" s="29">
+        <v>60.33</v>
+      </c>
+      <c r="G20" s="30">
+        <v>45917</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="28">
+        <v>57700000</v>
+      </c>
+      <c r="E21" s="28">
         <v>2</v>
       </c>
-      <c r="I2" s="21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9">
-      <c r="B3" s="17">
-        <v>88013235491</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2">
-        <v>57083060</v>
-      </c>
-      <c r="E3" s="2">
-        <v>202</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1508.28</v>
-      </c>
-      <c r="G3" s="3">
-        <v>45870</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
-      <c r="B4" s="17">
-        <v>88013235491</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2">
-        <v>57083060</v>
-      </c>
-      <c r="E4" s="2">
-        <v>202</v>
-      </c>
-      <c r="F4" s="1">
-        <v>100</v>
-      </c>
-      <c r="G4" s="3">
-        <v>45879</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9">
-      <c r="B5" s="17">
-        <v>88013235491</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2">
-        <v>57083060</v>
-      </c>
-      <c r="E5" s="2">
-        <v>202</v>
-      </c>
-      <c r="F5" s="1">
-        <v>99</v>
-      </c>
-      <c r="G5" s="3">
-        <v>45894</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="10"/>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="10"/>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="G9" s="3"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" spans="2:9" s="25" customFormat="1" ht="12">
-      <c r="B11" s="18"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="11"/>
-    </row>
-    <row r="12" spans="2:9">
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="G13" s="3"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" spans="2:9">
-      <c r="G14" s="3"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="10"/>
-    </row>
-    <row r="15" spans="2:9">
-      <c r="G15" s="3"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="10"/>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="G16" s="3"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="10"/>
-    </row>
-    <row r="17" spans="6:9">
-      <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="10"/>
-    </row>
-    <row r="18" spans="6:9">
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="10"/>
-    </row>
-    <row r="19" spans="6:9">
-      <c r="G19" s="3"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="10"/>
-    </row>
-    <row r="20" spans="6:9">
-      <c r="F20" s="8"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="21" spans="6:9">
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="10"/>
-    </row>
-    <row r="22" spans="6:9">
-      <c r="F22" s="9"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="10"/>
-    </row>
-    <row r="23" spans="6:9">
-      <c r="G23" s="3"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="10"/>
-    </row>
-    <row r="24" spans="6:9">
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="10"/>
-    </row>
-    <row r="25" spans="6:9">
-      <c r="G25" s="3"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="10"/>
-    </row>
-    <row r="26" spans="6:9">
-      <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="10"/>
-    </row>
-    <row r="27" spans="6:9">
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="10"/>
-    </row>
-    <row r="28" spans="6:9">
+      <c r="F21" s="29">
+        <v>346</v>
+      </c>
+      <c r="G21" s="30">
+        <v>45917</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="28">
+        <v>57160000</v>
+      </c>
+      <c r="E22" s="28">
+        <v>310</v>
+      </c>
+      <c r="F22" s="29">
+        <v>467.76</v>
+      </c>
+      <c r="G22" s="30">
+        <v>45918</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="28">
+        <v>57061410</v>
+      </c>
+      <c r="E23" s="28">
+        <v>296</v>
+      </c>
+      <c r="F23" s="29">
+        <v>52.04</v>
+      </c>
+      <c r="G23" s="30">
+        <v>45918</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="28">
+        <v>57038640</v>
+      </c>
+      <c r="E24" s="28">
+        <v>2650</v>
+      </c>
+      <c r="F24" s="29">
+        <v>349.19</v>
+      </c>
+      <c r="G24" s="30">
+        <v>45918</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="28">
+        <v>57036610</v>
+      </c>
+      <c r="E25" s="28">
+        <v>37</v>
+      </c>
+      <c r="F25" s="29">
+        <v>864.92</v>
+      </c>
+      <c r="G25" s="30">
+        <v>45918</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="28">
+        <v>57046001</v>
+      </c>
+      <c r="E26" s="28">
+        <v>0</v>
+      </c>
+      <c r="F26" s="29">
+        <v>321.81</v>
+      </c>
+      <c r="G26" s="30">
+        <v>45919</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27" s="22"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="21"/>
+    </row>
+    <row r="28" spans="2:9">
       <c r="G28" s="3"/>
       <c r="H28" s="4"/>
-      <c r="I28" s="10"/>
-    </row>
-    <row r="29" spans="6:9">
+      <c r="I28" s="6"/>
+    </row>
+    <row r="29" spans="2:9">
       <c r="G29" s="3"/>
       <c r="H29" s="4"/>
-      <c r="I29" s="10"/>
-    </row>
-    <row r="30" spans="6:9">
+      <c r="I29" s="6"/>
+    </row>
+    <row r="30" spans="2:9">
       <c r="G30" s="3"/>
       <c r="H30" s="4"/>
-      <c r="I30" s="10"/>
-    </row>
-    <row r="31" spans="6:9">
+      <c r="I30" s="6"/>
+    </row>
+    <row r="31" spans="2:9">
       <c r="G31" s="3"/>
       <c r="H31" s="4"/>
-      <c r="I31" s="10"/>
-    </row>
-    <row r="32" spans="6:9">
+      <c r="I31" s="6"/>
+    </row>
+    <row r="32" spans="2:9">
       <c r="G32" s="3"/>
       <c r="H32" s="4"/>
-      <c r="I32" s="10"/>
+      <c r="I32" s="6"/>
     </row>
     <row r="33" spans="7:9">
       <c r="G33" s="3"/>
       <c r="H33" s="4"/>
-      <c r="I33" s="10"/>
+      <c r="I33" s="6"/>
     </row>
     <row r="34" spans="7:9">
       <c r="G34" s="3"/>
       <c r="H34" s="4"/>
-      <c r="I34" s="10"/>
+      <c r="I34" s="6"/>
     </row>
     <row r="35" spans="7:9">
       <c r="G35" s="3"/>
       <c r="H35" s="4"/>
-      <c r="I35" s="10"/>
+      <c r="I35" s="6"/>
     </row>
     <row r="36" spans="7:9">
       <c r="G36" s="3"/>
       <c r="H36" s="4"/>
-      <c r="I36" s="10"/>
+      <c r="I36" s="6"/>
     </row>
     <row r="37" spans="7:9">
-      <c r="G37" s="3"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="10"/>
-    </row>
-    <row r="38" spans="7:9">
-      <c r="H38" s="2" t="s">
-        <v>6</v>
+      <c r="H37" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F2:I3 F6:I1048576">
-    <cfRule type="cellIs" dxfId="22" priority="11" operator="equal">
+  <conditionalFormatting sqref="F2:I1048575">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H3 H6:H1048576">
-    <cfRule type="cellIs" dxfId="21" priority="10" operator="equal">
+  <conditionalFormatting sqref="H1:H2">
+    <cfRule type="cellIs" dxfId="3" priority="11" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2">
-    <cfRule type="cellIs" dxfId="20" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="16" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3 H6:H10">
-    <cfRule type="cellIs" dxfId="19" priority="12" operator="equal">
+  <conditionalFormatting sqref="H2:H1048575">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:I4">
-    <cfRule type="cellIs" dxfId="18" priority="5" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:I5">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+  <conditionalFormatting sqref="H27:I27">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
